--- a/AAII_Financials/Quarterly/CRYCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CRYCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="92">
   <si>
     <t>CRYCY</t>
   </si>
@@ -656,69 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +763,17 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +807,17 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +851,17 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +875,11 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +913,17 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +957,17 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +1001,17 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +1045,17 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1066,11 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1104,17 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1148,17 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1172,11 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1210,17 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1254,17 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1298,17 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1342,17 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1386,17 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1430,17 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1474,17 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1518,17 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1562,17 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1606,17 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1650,17 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1694,17 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1738,17 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1782,17 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1826,17 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1870,66 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1943,11 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,43 +1961,55 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3110700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3033300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3200600</v>
+      </c>
+      <c r="G41" s="3">
         <v>2820500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>2818800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>2784500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>3093100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>3025600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>3269500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>3103800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>3183500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>2756100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>3070600</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1774,253 +2043,325 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9053400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>8872400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>8812500</v>
+      </c>
+      <c r="G43" s="3">
         <v>8765900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>8487100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>8349200</v>
       </c>
-      <c r="G43" s="3">
-        <v>8434900</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
+        <v>8622600</v>
+      </c>
+      <c r="K43" s="3">
         <v>9094500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>8651400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>8789400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>8931900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>9268100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>9127200</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>557100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>553800</v>
+      </c>
+      <c r="F44" s="3">
+        <v>479200</v>
+      </c>
+      <c r="G44" s="3">
         <v>577900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>534700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>586600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>473200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>541500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>500500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>519700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>452200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>405400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>409600</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>366100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>351300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>309300</v>
+      </c>
+      <c r="G45" s="3">
         <v>386100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>576200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>413100</v>
       </c>
-      <c r="G45" s="3">
-        <v>480400</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
+        <v>292700</v>
+      </c>
+      <c r="K45" s="3">
         <v>360200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>308400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>302600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>478000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>296900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>341400</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13091600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>12810800</v>
+      </c>
+      <c r="F46" s="3">
+        <v>12805600</v>
+      </c>
+      <c r="G46" s="3">
         <v>12550400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>12418000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>12133300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>12481800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>13021900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>12730000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>12715400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>13046200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>12726600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>12948800</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>583500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>562300</v>
+      </c>
+      <c r="F47" s="3">
+        <v>550800</v>
+      </c>
+      <c r="G47" s="3">
         <v>528000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>521300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>512400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="J47" s="3">
         <v>451100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>457800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>429000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>421900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>427100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>407400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>404100</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>877000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>875800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>863100</v>
+      </c>
+      <c r="G48" s="3">
         <v>825300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>815700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>806900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>807600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>820300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>771900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>777600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>796500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>766500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>768300</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>397800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>400400</v>
+      </c>
+      <c r="F49" s="3">
+        <v>405300</v>
+      </c>
+      <c r="G49" s="3">
         <v>380300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>385800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>389200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>395900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>401900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>380600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>403000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>404800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>383100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>385000</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2395,17 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2439,61 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2138900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2129200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2140400</v>
+      </c>
+      <c r="G52" s="3">
         <v>1844200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>1868200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>2045400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>1905200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>1991700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>1893600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>1925500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>1995200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>1686800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>1757800</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2527,61 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17263600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16937400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>16916600</v>
+      </c>
+      <c r="G54" s="3">
         <v>16246500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>16124100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>15994900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>16151400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>16805500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>16313500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>16352900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>16780700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>16074400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>16370100</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2595,11 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2613,275 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5730800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5571300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>5849200</v>
+      </c>
+      <c r="G57" s="3">
         <v>5556100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>5663900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
         <v>5940900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="J57" s="3">
         <v>6098200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>6576900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>6353700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>6727500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>7204400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>6898700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>6976500</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>93500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>88900</v>
+      </c>
+      <c r="G58" s="3">
         <v>57000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>46100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>51500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>40300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>60200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>136300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>64000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>402000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>368600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>440000</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2291800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2213600</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2051600</v>
+      </c>
+      <c r="G59" s="3">
         <v>2171600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>2173100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>1970300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>2279600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>2437400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>2388600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>2044400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>1544000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>1529700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>1683100</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8291000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8000700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>8205800</v>
+      </c>
+      <c r="G60" s="3">
         <v>7919900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>8097400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>8082700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>8661900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>9205900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>9056300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>8941400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>9342100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>8907800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>9264100</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1126400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1116200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1088800</v>
+      </c>
+      <c r="G61" s="3">
         <v>1057100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>858600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>755900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>467500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>440200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>412400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>420200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>430700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>433100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>435900</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>88900</v>
+        <v>10500</v>
       </c>
       <c r="E62" s="3">
-        <v>92900</v>
+        <v>6600</v>
       </c>
       <c r="F62" s="3">
-        <v>85600</v>
+        <v>10500</v>
       </c>
       <c r="G62" s="3">
         <v>88900</v>
       </c>
       <c r="H62" s="3">
+        <v>92900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>85600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K62" s="3">
         <v>6200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>84800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>81700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>83000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>11200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>87100</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2915,17 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2959,17 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +3003,61 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9543300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9238000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>9414800</v>
+      </c>
+      <c r="G66" s="3">
         <v>9092600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>9075000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>8949700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>9241600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>9759900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>9579400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>9479500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>9888100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>9452600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>9820900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +3071,11 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +3109,17 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +3153,17 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +3197,17 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +3241,61 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3005700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3084800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>2967500</v>
+      </c>
+      <c r="G72" s="3">
         <v>2735600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="H72" s="3">
         <v>2616900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
         <v>2686300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>2593000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>2552400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>2361900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>2488700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>2448900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>2269400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>2185800</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +3329,17 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3373,17 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3417,61 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7286500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7304900</v>
+      </c>
+      <c r="F76" s="3">
+        <v>7126100</v>
+      </c>
+      <c r="G76" s="3">
         <v>6823400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>6678600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>6700400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>6579600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>6756100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>6413300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>6572800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>6601700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>6312900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>6241400</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3505,66 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3598,17 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3622,55 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
+        <v>66700</v>
+      </c>
+      <c r="G83" s="3">
         <v>-50400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>33000</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>71000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>-46300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>31100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>60700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>-44200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>32400</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3704,17 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3748,17 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3792,17 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3836,17 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3880,61 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-201800</v>
+      </c>
+      <c r="F89" s="3">
+        <v>351200</v>
+      </c>
+      <c r="G89" s="3">
         <v>92000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-57200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-550700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>251500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>61000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>122500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>288400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>403200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>9600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>60200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3948,55 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-17200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-13500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-48600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-44500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-15600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-10800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-55200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-14500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-12700</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +4030,17 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +4074,61 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-271700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-145700</v>
+      </c>
+      <c r="G94" s="3">
         <v>-168800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>-52400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>64900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>202600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-226800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-73000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>7700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-186000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>136700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-217100</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +4142,55 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F96" s="3">
+        <v>15400</v>
+      </c>
+      <c r="G96" s="3">
         <v>257400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
         <v>6500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="I96" s="3">
         <v>5100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="J96" s="3">
         <v>18300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="K96" s="3">
         <v>252700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="L96" s="3">
         <v>7100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="M96" s="3">
         <v>7100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="N96" s="3">
         <v>37800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="O96" s="3">
         <v>230400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="P96" s="3">
         <v>13500</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +4224,17 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +4268,17 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +4312,145 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F100" s="3">
+        <v>31300</v>
+      </c>
+      <c r="G100" s="3">
         <v>-106000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>73600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>300900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>-22000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-338700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>61000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-300100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-55000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-280300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-7000</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>7900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-212200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-226600</v>
+      </c>
+      <c r="F102" s="3">
+        <v>236300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-183000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-35400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-184700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>431800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-504700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>110500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-4000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>162300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-134900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-162000</v>
       </c>
     </row>
